--- a/public/schedule_template.xlsx
+++ b/public/schedule_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21274" windowHeight="9317"/>
+    <workbookView windowWidth="21274" windowHeight="8717"/>
   </bookViews>
   <sheets>
     <sheet name="第一周" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="17">
   <si>
     <t>新 闻 嗅 觉 图 片 社 第 x 周 排 班 表</t>
   </si>
@@ -39,6 +39,9 @@
   </si>
   <si>
     <t>一二节</t>
+  </si>
+  <si>
+    <t>"----"</t>
   </si>
   <si>
     <t>三四节</t>
@@ -778,7 +781,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -824,9 +827,6 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -838,9 +838,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1485,11 +1482,17 @@
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="9"/>
+      <c r="B6" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="C6" s="10"/>
-      <c r="D6" s="9"/>
+      <c r="D6" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E6" s="10"/>
-      <c r="F6" s="9"/>
+      <c r="F6" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="G6" s="11"/>
       <c r="J6"/>
       <c r="K6"/>
@@ -1513,13 +1516,19 @@
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:14">
       <c r="A8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="9"/>
+        <v>9</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="C8" s="10"/>
-      <c r="D8" s="9"/>
+      <c r="D8" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E8" s="10"/>
-      <c r="F8" s="9"/>
+      <c r="F8" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="G8" s="11"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1557,13 +1566,19 @@
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:14">
       <c r="A11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="9"/>
+        <v>10</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="16"/>
+      <c r="F11" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="G11" s="11"/>
       <c r="J11"/>
       <c r="K11"/>
@@ -1573,10 +1588,10 @@
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:14">
       <c r="A12" s="4"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="18"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="17"/>
       <c r="D12" s="9"/>
-      <c r="E12" s="19"/>
+      <c r="E12" s="18"/>
       <c r="F12" s="9"/>
       <c r="G12" s="13"/>
       <c r="J12"/>
@@ -1587,13 +1602,19 @@
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:14">
       <c r="A13" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="9"/>
+        <v>11</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="16"/>
+      <c r="F13" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="G13" s="11"/>
       <c r="J13"/>
       <c r="K13"/>
@@ -1603,10 +1624,10 @@
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:14">
       <c r="A14" s="4"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="18"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="17"/>
       <c r="D14" s="9"/>
-      <c r="E14" s="19"/>
+      <c r="E14" s="18"/>
       <c r="F14" s="9"/>
       <c r="G14" s="13"/>
       <c r="J14"/>
@@ -1616,13 +1637,13 @@
       <c r="N14"/>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:14">
-      <c r="A15" s="21"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
       <c r="J15"/>
       <c r="K15"/>
       <c r="L15"/>
@@ -1630,21 +1651,21 @@
       <c r="N15"/>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:14">
-      <c r="A16" s="21"/>
+      <c r="A16" s="19"/>
       <c r="B16" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>4</v>
@@ -1659,11 +1680,17 @@
       <c r="A17" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="9"/>
+      <c r="B17" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="C17" s="10"/>
-      <c r="D17" s="9"/>
+      <c r="D17" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E17" s="10"/>
-      <c r="F17" s="20"/>
+      <c r="F17" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="G17" s="11"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -1677,7 +1704,7 @@
       <c r="C18" s="12"/>
       <c r="D18" s="9"/>
       <c r="E18" s="12"/>
-      <c r="F18" s="20"/>
+      <c r="F18" s="9"/>
       <c r="G18" s="13"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1687,13 +1714,19 @@
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:14">
       <c r="A19" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="9"/>
+        <v>9</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="20"/>
+      <c r="D19" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E19" s="10"/>
-      <c r="F19" s="20"/>
+      <c r="F19" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="G19" s="11"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1704,10 +1737,10 @@
     <row r="20" ht="48" customHeight="1" spans="1:14">
       <c r="A20" s="4"/>
       <c r="B20" s="9"/>
-      <c r="C20" s="23"/>
+      <c r="C20" s="21"/>
       <c r="D20" s="9"/>
       <c r="E20" s="12"/>
-      <c r="F20" s="20"/>
+      <c r="F20" s="9"/>
       <c r="G20" s="13"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -1717,7 +1750,7 @@
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:14">
       <c r="A21" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
@@ -1733,13 +1766,19 @@
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:14">
       <c r="A22" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B22" s="9"/>
+        <v>10</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="C22" s="10"/>
-      <c r="D22" s="9"/>
+      <c r="D22" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E22" s="10"/>
-      <c r="F22" s="20"/>
+      <c r="F22" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="G22" s="10"/>
       <c r="J22"/>
       <c r="K22"/>
@@ -1753,7 +1792,7 @@
       <c r="C23" s="12"/>
       <c r="D23" s="9"/>
       <c r="E23" s="12"/>
-      <c r="F23" s="20"/>
+      <c r="F23" s="9"/>
       <c r="G23" s="12"/>
       <c r="J23"/>
       <c r="K23"/>
@@ -1763,15 +1802,21 @@
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:14">
       <c r="A24" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B24" s="9"/>
+        <v>11</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="C24" s="10"/>
-      <c r="D24" s="9"/>
+      <c r="D24" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E24" s="10"/>
-      <c r="F24" s="20"/>
+      <c r="F24" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="G24" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J24"/>
       <c r="K24"/>
@@ -1785,7 +1830,7 @@
       <c r="C25" s="12"/>
       <c r="D25" s="9"/>
       <c r="E25" s="12"/>
-      <c r="F25" s="20"/>
+      <c r="F25" s="9"/>
       <c r="G25" s="12"/>
       <c r="J25"/>
       <c r="K25"/>
@@ -1794,13 +1839,13 @@
       <c r="N25"/>
     </row>
     <row r="26" customHeight="1" spans="1:14">
-      <c r="A26" s="24"/>
-      <c r="B26" s="25"/>
-      <c r="C26" s="24"/>
+      <c r="A26" s="22"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="22"/>
       <c r="D26"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="24"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
       <c r="J26"/>
       <c r="K26"/>
       <c r="L26"/>
@@ -1808,13 +1853,13 @@
       <c r="N26"/>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="24"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="24"/>
+      <c r="A27" s="22"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
       <c r="J27"/>
       <c r="K27"/>
       <c r="L27"/>
@@ -1822,13 +1867,13 @@
       <c r="N27"/>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="24"/>
-      <c r="B28" s="25"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="24"/>
+      <c r="A28" s="22"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
       <c r="J28"/>
       <c r="K28"/>
       <c r="L28"/>
@@ -1836,13 +1881,13 @@
       <c r="N28"/>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" s="24"/>
-      <c r="B29" s="25"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
+      <c r="A29" s="22"/>
+      <c r="B29" s="23"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
       <c r="J29"/>
       <c r="K29"/>
       <c r="L29"/>
@@ -1850,13 +1895,13 @@
       <c r="N29"/>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="24"/>
-      <c r="B30" s="25"/>
-      <c r="C30" s="24"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="24"/>
-      <c r="G30" s="24"/>
+      <c r="A30" s="22"/>
+      <c r="B30" s="23"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
       <c r="J30"/>
       <c r="K30"/>
       <c r="L30"/>
